--- a/results/GSE186332/selinexor_proliferation_sensitivity_analysis.xlsx
+++ b/results/GSE186332/selinexor_proliferation_sensitivity_analysis.xlsx
@@ -633,19 +633,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.7666451703313775</v>
+        <v>-0.7666451703313774</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4645690067847101</v>
+        <v>0.4645690067847102</v>
       </c>
       <c r="D2" t="n">
         <v>0.2354465298658576</v>
       </c>
       <c r="E2" t="n">
-        <v>0.916659770640472</v>
+        <v>0.9166597706404721</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02704162110085874</v>
+        <v>0.02704162110085877</v>
       </c>
     </row>
     <row r="3">
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3035692459935511</v>
+        <v>0.3035692459935508</v>
       </c>
       <c r="C2" t="n">
         <v>-0.4858150606256127</v>
       </c>
       <c r="D2" t="n">
-        <v>1.890327821111403</v>
+        <v>1.890327821111402</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -811,13 +811,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.09053496729843569</v>
+        <v>-0.09053496729843558</v>
       </c>
       <c r="C3" t="n">
         <v>-1.437721802399025</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1536022691023406</v>
+        <v>0.1536022691023411</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>0.3988564445182058</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5669879424213801</v>
+        <v>-0.5669879424213802</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.325687326512341</v>
+        <v>-0.3256873265123409</v>
       </c>
       <c r="C7" t="n">
         <v>0.7938781950718534</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8826594532747007</v>
+        <v>-0.8826594532747005</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>-0.5746463972119965</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4443135750350134</v>
+        <v>0.4443135750350135</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.3785271549791805</v>
+        <v>-0.3785271549791804</v>
       </c>
       <c r="C12" t="n">
         <v>-0.2161332986651115</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.115512280438328</v>
+        <v>-1.115512280438327</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.5012702603247939</v>
+        <v>-0.5012702603247938</v>
       </c>
       <c r="C13" t="n">
         <v>0.9015926609919137</v>
@@ -1363,13 +1363,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1669232286961848</v>
+        <v>-0.1669232286961846</v>
       </c>
       <c r="C15" t="n">
         <v>0.3778066907030854</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1830230217943296</v>
+        <v>-0.1830230217943289</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.2148486011203608</v>
+        <v>-0.2148486011203609</v>
       </c>
       <c r="C16" t="n">
         <v>1.819469531538429</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3942189848705998</v>
+        <v>-0.3942189848706001</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.3855596391587646</v>
+        <v>-0.3855596391587647</v>
       </c>
       <c r="C17" t="n">
         <v>0.1998335158287886</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.14650280161739</v>
+        <v>-1.146502801617391</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.06489355131175112</v>
+        <v>-0.06489355131175117</v>
       </c>
       <c r="C18" t="n">
         <v>0.4757315244629794</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2665980220829754</v>
+        <v>0.2665980220829752</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>0.7294218893112417</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7903590860383858</v>
+        <v>0.7903590860383859</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1456968949337566</v>
+        <v>-0.1456968949337565</v>
       </c>
       <c r="C20" t="n">
         <v>0.5691912134699814</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.08948350869765191</v>
+        <v>-0.08948350869765143</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1777,13 +1777,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3795170631755898</v>
+        <v>-0.3795170631755896</v>
       </c>
       <c r="C24" t="n">
         <v>0.1696529135920411</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.119874575488377</v>
+        <v>-1.119874575488376</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1823,13 +1823,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1197571205511969</v>
+        <v>0.1197571205511967</v>
       </c>
       <c r="C25" t="n">
         <v>-0.2268099651610779</v>
       </c>
       <c r="D25" t="n">
-        <v>1.080310561061668</v>
+        <v>1.080310561061667</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1869,13 +1869,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.3263959549847679</v>
+        <v>-0.3263959549847678</v>
       </c>
       <c r="C26" t="n">
         <v>0.2118292645818077</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8857822140406026</v>
+        <v>-0.8857822140406025</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3409314871343583</v>
+        <v>-0.3409314871343582</v>
       </c>
       <c r="C27" t="n">
         <v>-0.1689490894384822</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9498369215134704</v>
+        <v>-0.9498369215134701</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2007,13 +2007,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1461892299385081</v>
+        <v>-0.146189229938508</v>
       </c>
       <c r="C29" t="n">
         <v>-0.02968559881833521</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.09165311448734394</v>
+        <v>-0.0916531144873437</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1957735252430408</v>
+        <v>-0.1957735252430409</v>
       </c>
       <c r="C30" t="n">
         <v>-0.0006623959568772099</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3101595646326613</v>
+        <v>-0.3101595646326616</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>0.4961157560071276</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7243883580184677</v>
+        <v>-0.724388358018468</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>0.2351879475633289</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.06676696903508038</v>
+        <v>-0.06676696903508014</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.09783912785934074</v>
+        <v>-0.09783912785934062</v>
       </c>
       <c r="C33" t="n">
         <v>0.3038667126524351</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1214145333353488</v>
+        <v>0.1214145333353493</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>0.6215138439426001</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7129966652452814</v>
+        <v>-0.7129966652452815</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>0.6271730023339054</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4845703340344917</v>
+        <v>-0.4845703340344918</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>-0.720307529875688</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5569933730109207</v>
+        <v>0.5569933730109208</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2467,13 +2467,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.01875336389815385</v>
+        <v>-0.0187533638981538</v>
       </c>
       <c r="C39" t="n">
         <v>-0.1178819236882987</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4699270902660449</v>
+        <v>0.4699270902660452</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.2386366811022367</v>
+        <v>0.2386366811022368</v>
       </c>
       <c r="C40" t="n">
         <v>-0.364682101986727</v>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1768006485748422</v>
+        <v>0.1768006485748421</v>
       </c>
       <c r="C41" t="n">
         <v>-0.6530130464183399</v>
@@ -2611,7 +2611,7 @@
         <v>-0.5887043434061376</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0002558880407976535</v>
+        <v>0.0002558880407978982</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>1.332978640440253</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2068886854809438</v>
+        <v>-0.2068886854809436</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2518575374672229</v>
+        <v>0.2518575374672231</v>
       </c>
       <c r="C44" t="n">
         <v>-0.4562099652541439</v>
       </c>
       <c r="D44" t="n">
-        <v>1.662446355989434</v>
+        <v>1.662446355989435</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.1266908976462645</v>
+        <v>-0.1266908976462644</v>
       </c>
       <c r="C45" t="n">
         <v>-0.3099088589278771</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.005728501729108614</v>
+        <v>-0.00572850172910837</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2835,13 +2835,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.02074949506060786</v>
+        <v>-0.02074949506060797</v>
       </c>
       <c r="C47" t="n">
         <v>-0.1120333472702057</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4611306047729376</v>
+        <v>0.4611306047729372</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2881,13 +2881,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.2729567360682781</v>
+        <v>-0.272956736068278</v>
       </c>
       <c r="C48" t="n">
         <v>0.4113340895852979</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6502880126555679</v>
+        <v>-0.6502880126555675</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>0.1544321174350495</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.6321605150517656</v>
+        <v>-0.6321605150517657</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>-0.1613341681448813</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.9818298904967256</v>
+        <v>-0.9818298904967258</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>0.3979531232292181</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.9013512936456987</v>
+        <v>-0.9013512936456988</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>

--- a/results/GSE186332/selinexor_proliferation_sensitivity_analysis.xlsx
+++ b/results/GSE186332/selinexor_proliferation_sensitivity_analysis.xlsx
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2657921177348192</v>
+        <v>0.2657921177348191</v>
       </c>
     </row>
     <row r="10">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.10170073758894</v>
+        <v>0.1017007375889399</v>
       </c>
     </row>
     <row r="11">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07046904484761007</v>
+        <v>0.07046904484761005</v>
       </c>
     </row>
     <row r="14">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01203558210646721</v>
+        <v>0.0120355821064672</v>
       </c>
     </row>
     <row r="15">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.003263680692093943</v>
+        <v>0.00326368069209395</v>
       </c>
     </row>
   </sheetData>
@@ -633,19 +633,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.7666451703313774</v>
+        <v>-0.7666451703313775</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4645690067847102</v>
+        <v>0.4645690067847101</v>
       </c>
       <c r="D2" t="n">
         <v>0.2354465298658576</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9166597706404721</v>
+        <v>0.916659770640472</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02704162110085877</v>
+        <v>0.02704162110085874</v>
       </c>
     </row>
     <row r="3">
@@ -658,10 +658,10 @@
         <v>-1.325040788015471</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2657921177348192</v>
+        <v>0.2657921177348191</v>
       </c>
       <c r="D3" t="n">
-        <v>0.10170073758894</v>
+        <v>0.1017007375889399</v>
       </c>
       <c r="E3" t="n">
         <v>0.694640486635396</v>
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-2.652581745763584</v>
+        <v>-2.652581745763585</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07046904484761007</v>
+        <v>0.07046904484761005</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01203558210646721</v>
+        <v>0.0120355821064672</v>
       </c>
       <c r="E4" t="n">
         <v>0.4126004241262339</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003263680692093943</v>
+        <v>0.00326368069209395</v>
       </c>
     </row>
   </sheetData>
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3035692459935508</v>
+        <v>0.303569245993551</v>
       </c>
       <c r="C2" t="n">
         <v>-0.4858150606256127</v>
       </c>
       <c r="D2" t="n">
-        <v>1.890327821111402</v>
+        <v>1.890327821111403</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -811,13 +811,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.09053496729843558</v>
+        <v>-0.09053496729843552</v>
       </c>
       <c r="C3" t="n">
         <v>-1.437721802399025</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1536022691023411</v>
+        <v>0.1536022691023414</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.0006384040292134463</v>
+        <v>-0.0006384040292133353</v>
       </c>
       <c r="C4" t="n">
         <v>0.1791872673190783</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5497555026933404</v>
+        <v>0.5497555026933409</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.2540539747143987</v>
+        <v>-0.2540539747143988</v>
       </c>
       <c r="C6" t="n">
         <v>0.3988564445182058</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5669879424213802</v>
+        <v>-0.566987942421381</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.3256873265123409</v>
+        <v>-0.325687326512341</v>
       </c>
       <c r="C7" t="n">
         <v>0.7938781950718534</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8826594532747005</v>
+        <v>-0.8826594532747009</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.190930439496977</v>
+        <v>0.1909304394969769</v>
       </c>
       <c r="C8" t="n">
         <v>-1.009660671247483</v>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02456567791523656</v>
+        <v>-0.02456567791523645</v>
       </c>
       <c r="C9" t="n">
         <v>-0.5746463972119965</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4443135750350135</v>
+        <v>0.444313575035014</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.3785271549791804</v>
+        <v>-0.3785271549791803</v>
       </c>
       <c r="C12" t="n">
         <v>-0.2161332986651115</v>
@@ -1363,13 +1363,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1669232286961846</v>
+        <v>-0.1669232286961848</v>
       </c>
       <c r="C15" t="n">
         <v>0.3778066907030854</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1830230217943289</v>
+        <v>-0.1830230217943294</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>1.819469531538429</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3942189848706001</v>
+        <v>-0.3942189848706004</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.3855596391587647</v>
+        <v>-0.3855596391587646</v>
       </c>
       <c r="C17" t="n">
         <v>0.1998335158287886</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.146502801617391</v>
+        <v>-1.14650280161739</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1456968949337565</v>
+        <v>-0.1456968949337566</v>
       </c>
       <c r="C20" t="n">
         <v>0.5691912134699814</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.08948350869765143</v>
+        <v>-0.08948350869765193</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.285845185822498</v>
+        <v>0.2858451858224979</v>
       </c>
       <c r="C21" t="n">
         <v>-0.5258996276885851</v>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.191567206592782</v>
+        <v>0.1915672065927821</v>
       </c>
       <c r="C23" t="n">
         <v>-1.546183152102437</v>
@@ -1777,13 +1777,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3795170631755896</v>
+        <v>-0.3795170631755898</v>
       </c>
       <c r="C24" t="n">
         <v>0.1696529135920411</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.119874575488376</v>
+        <v>-1.119874575488377</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1823,13 +1823,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1197571205511967</v>
+        <v>0.1197571205511969</v>
       </c>
       <c r="C25" t="n">
         <v>-0.2268099651610779</v>
       </c>
       <c r="D25" t="n">
-        <v>1.080310561061667</v>
+        <v>1.080310561061668</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2897718616821827</v>
+        <v>-0.2897718616821826</v>
       </c>
       <c r="C31" t="n">
         <v>0.4961157560071276</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.724388358018468</v>
+        <v>-0.7243883580184676</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2145,13 +2145,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1405419733734229</v>
+        <v>-0.1405419733734231</v>
       </c>
       <c r="C32" t="n">
         <v>0.2351879475633289</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.06676696903508014</v>
+        <v>-0.06676696903508088</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.09783912785934062</v>
+        <v>-0.09783912785934074</v>
       </c>
       <c r="C33" t="n">
         <v>0.3038667126524351</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1214145333353493</v>
+        <v>0.1214145333353489</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2421,13 +2421,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.001004040388167093</v>
+        <v>0.001004040388167204</v>
       </c>
       <c r="C38" t="n">
         <v>-0.720307529875688</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5569933730109208</v>
+        <v>0.5569933730109212</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2467,13 +2467,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.0187533638981538</v>
+        <v>-0.01875336389815396</v>
       </c>
       <c r="C39" t="n">
         <v>-0.1178819236882987</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4699270902660452</v>
+        <v>0.4699270902660445</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.2386366811022368</v>
+        <v>0.2386366811022366</v>
       </c>
       <c r="C40" t="n">
         <v>-0.364682101986727</v>
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.1253328976907889</v>
+        <v>-0.125332897690789</v>
       </c>
       <c r="C42" t="n">
         <v>-0.5887043434061376</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0002558880407978982</v>
+        <v>0.0002558880407971643</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>1.332978640440253</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2068886854809436</v>
+        <v>-0.2068886854809439</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2518575374672231</v>
+        <v>0.2518575374672232</v>
       </c>
       <c r="C44" t="n">
         <v>-0.4562099652541439</v>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.1266908976462644</v>
+        <v>-0.1266908976462645</v>
       </c>
       <c r="C45" t="n">
         <v>-0.3099088589278771</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.00572850172910837</v>
+        <v>-0.005728501729108615</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2835,13 +2835,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.02074949506060797</v>
+        <v>-0.02074949506060786</v>
       </c>
       <c r="C47" t="n">
         <v>-0.1120333472702057</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4611306047729372</v>
+        <v>0.4611306047729377</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2881,13 +2881,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.272956736068278</v>
+        <v>-0.2729567360682781</v>
       </c>
       <c r="C48" t="n">
         <v>0.4113340895852979</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6502880126555675</v>
+        <v>-0.6502880126555679</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>-0.09787546261339235</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.492094818603322</v>
+        <v>-1.492094818603323</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -3065,13 +3065,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.3481914504932407</v>
+        <v>-0.3481914504932406</v>
       </c>
       <c r="C52" t="n">
         <v>-0.1613341681448813</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.9818298904967258</v>
+        <v>-0.9818298904967252</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>

--- a/results/GSE186332/selinexor_proliferation_sensitivity_analysis.xlsx
+++ b/results/GSE186332/selinexor_proliferation_sensitivity_analysis.xlsx
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2657921177348191</v>
+        <v>0.2657921177348193</v>
       </c>
     </row>
     <row r="10">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1017007375889399</v>
+        <v>0.10170073758894</v>
       </c>
     </row>
     <row r="11">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.694640486635396</v>
+        <v>0.6946404866353961</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07046904484761005</v>
+        <v>0.0704690448476101</v>
       </c>
     </row>
     <row r="14">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0120355821064672</v>
+        <v>0.01203558210646722</v>
       </c>
     </row>
     <row r="15">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.00326368069209395</v>
+        <v>0.003263680692093936</v>
       </c>
     </row>
   </sheetData>
@@ -658,13 +658,13 @@
         <v>-1.325040788015471</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2657921177348191</v>
+        <v>0.2657921177348193</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1017007375889399</v>
+        <v>0.10170073758894</v>
       </c>
       <c r="E3" t="n">
-        <v>0.694640486635396</v>
+        <v>0.6946404866353961</v>
       </c>
       <c r="F3" t="n">
         <v>0.006864912721262834</v>
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-2.652581745763585</v>
+        <v>-2.652581745763584</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07046904484761005</v>
+        <v>0.0704690448476101</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0120355821064672</v>
+        <v>0.01203558210646722</v>
       </c>
       <c r="E4" t="n">
         <v>0.4126004241262339</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00326368069209395</v>
+        <v>0.003263680692093936</v>
       </c>
     </row>
   </sheetData>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.303569245993551</v>
+        <v>0.3035692459935509</v>
       </c>
       <c r="C2" t="n">
         <v>-0.4858150606256127</v>
@@ -811,13 +811,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.09053496729843552</v>
+        <v>-0.09053496729843558</v>
       </c>
       <c r="C3" t="n">
         <v>-1.437721802399025</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1536022691023414</v>
+        <v>0.1536022691023411</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.0006384040292133353</v>
+        <v>-0.0006384040292134463</v>
       </c>
       <c r="C4" t="n">
         <v>0.1791872673190783</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5497555026933409</v>
+        <v>0.5497555026933404</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3490853798274803</v>
+        <v>0.3490853798274802</v>
       </c>
       <c r="C5" t="n">
         <v>-0.6128078723550465</v>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.2540539747143988</v>
+        <v>-0.2540539747143989</v>
       </c>
       <c r="C6" t="n">
         <v>0.3988564445182058</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.566987942421381</v>
+        <v>-0.5669879424213812</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>0.06590635973753277</v>
       </c>
       <c r="D10" t="n">
-        <v>1.019099448631347</v>
+        <v>1.019099448631348</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.3621064211877677</v>
+        <v>-0.3621064211877676</v>
       </c>
       <c r="C11" t="n">
         <v>-0.3029434700678931</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.043149928054248</v>
+        <v>-1.043149928054247</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.3785271549791803</v>
+        <v>-0.3785271549791804</v>
       </c>
       <c r="C12" t="n">
         <v>-0.2161332986651115</v>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.5012702603247938</v>
+        <v>-0.5012702603247937</v>
       </c>
       <c r="C13" t="n">
         <v>0.9015926609919137</v>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.4000280024741703</v>
+        <v>-0.4000280024741704</v>
       </c>
       <c r="C14" t="n">
         <v>0.5547723214630254</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.210261511669543</v>
+        <v>-1.210261511669544</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1363,13 +1363,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1669232286961848</v>
+        <v>-0.1669232286961847</v>
       </c>
       <c r="C15" t="n">
         <v>0.3778066907030854</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1830230217943294</v>
+        <v>-0.1830230217943291</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.06489355131175117</v>
+        <v>-0.06489355131175095</v>
       </c>
       <c r="C18" t="n">
         <v>0.4757315244629794</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2665980220829752</v>
+        <v>0.2665980220829762</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.05396025482033245</v>
+        <v>0.0539602548203324</v>
       </c>
       <c r="C19" t="n">
         <v>0.7294218893112417</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7903590860383859</v>
+        <v>0.7903590860383856</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2858451858224979</v>
+        <v>0.285845185822498</v>
       </c>
       <c r="C21" t="n">
         <v>-0.5258996276885851</v>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1989128906978094</v>
+        <v>-0.1989128906978095</v>
       </c>
       <c r="C22" t="n">
         <v>0.3462135391995458</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3239940175984092</v>
+        <v>-0.3239940175984097</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1915672065927821</v>
+        <v>0.191567206592782</v>
       </c>
       <c r="C23" t="n">
         <v>-1.546183152102437</v>
@@ -1777,13 +1777,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3795170631755898</v>
+        <v>-0.3795170631755896</v>
       </c>
       <c r="C24" t="n">
         <v>0.1696529135920411</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.119874575488377</v>
+        <v>-1.119874575488376</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3409314871343582</v>
+        <v>-0.3409314871343583</v>
       </c>
       <c r="C27" t="n">
         <v>-0.1689490894384822</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9498369215134701</v>
+        <v>-0.9498369215134705</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2007,13 +2007,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.146189229938508</v>
+        <v>-0.1461892299385081</v>
       </c>
       <c r="C29" t="n">
         <v>-0.02968559881833521</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0916531144873437</v>
+        <v>-0.09165311448734419</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2897718616821826</v>
+        <v>-0.2897718616821827</v>
       </c>
       <c r="C31" t="n">
         <v>0.4961157560071276</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7243883580184676</v>
+        <v>-0.724388358018468</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2145,13 +2145,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1405419733734231</v>
+        <v>-0.1405419733734229</v>
       </c>
       <c r="C32" t="n">
         <v>0.2351879475633289</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.06676696903508088</v>
+        <v>-0.06676696903508014</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.09783912785934074</v>
+        <v>-0.09783912785934068</v>
       </c>
       <c r="C33" t="n">
         <v>0.3038667126524351</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1214145333353489</v>
+        <v>0.1214145333353491</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.1537779986546591</v>
+        <v>0.153777998654659</v>
       </c>
       <c r="C35" t="n">
         <v>-0.8821813456855014</v>
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.2353514648807942</v>
+        <v>-0.2353514648807941</v>
       </c>
       <c r="C37" t="n">
         <v>0.6271730023339054</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4845703340344918</v>
+        <v>-0.4845703340344913</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2421,13 +2421,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.001004040388167204</v>
+        <v>0.001004040388167038</v>
       </c>
       <c r="C38" t="n">
         <v>-0.720307529875688</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5569933730109212</v>
+        <v>0.5569933730109206</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2467,13 +2467,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.01875336389815396</v>
+        <v>-0.01875336389815391</v>
       </c>
       <c r="C39" t="n">
         <v>-0.1178819236882987</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4699270902660445</v>
+        <v>0.4699270902660447</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.2386366811022366</v>
+        <v>0.2386366811022367</v>
       </c>
       <c r="C40" t="n">
         <v>-0.364682101986727</v>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1768006485748421</v>
+        <v>0.176800648574842</v>
       </c>
       <c r="C41" t="n">
         <v>-0.6530130464183399</v>
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.125332897690789</v>
+        <v>-0.1253328976907889</v>
       </c>
       <c r="C42" t="n">
         <v>-0.5887043434061376</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0002558880407971643</v>
+        <v>0.0002558880407976535</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2518575374672232</v>
+        <v>0.251857537467223</v>
       </c>
       <c r="C44" t="n">
         <v>-0.4562099652541439</v>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.1266908976462645</v>
+        <v>-0.1266908976462644</v>
       </c>
       <c r="C45" t="n">
         <v>-0.3099088589278771</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.005728501729108615</v>
+        <v>-0.00572850172910837</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2789,13 +2789,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.1656100261516483</v>
+        <v>-0.1656100261516482</v>
       </c>
       <c r="C46" t="n">
         <v>0.07426114607454079</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1772360437891739</v>
+        <v>-0.1772360437891734</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2835,13 +2835,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.02074949506060786</v>
+        <v>-0.02074949506060797</v>
       </c>
       <c r="C47" t="n">
         <v>-0.1120333472702057</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4611306047729377</v>
+        <v>0.4611306047729372</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.4531076962497638</v>
+        <v>-0.4531076962497637</v>
       </c>
       <c r="C49" t="n">
         <v>0.8190497906720144</v>
       </c>
       <c r="D49" t="n">
-        <v>-1.444171369427372</v>
+        <v>-1.444171369427371</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -3065,13 +3065,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.3481914504932406</v>
+        <v>-0.3481914504932407</v>
       </c>
       <c r="C52" t="n">
         <v>-0.1613341681448813</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.9818298904967252</v>
+        <v>-0.9818298904967258</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>

--- a/results/GSE186332/selinexor_proliferation_sensitivity_analysis.xlsx
+++ b/results/GSE186332/selinexor_proliferation_sensitivity_analysis.xlsx
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2657921177348193</v>
+        <v>0.2657921177348191</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6946404866353961</v>
+        <v>0.6946404866353959</v>
       </c>
     </row>
     <row r="12">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.006864912721262834</v>
+        <v>0.006864912721262829</v>
       </c>
     </row>
     <row r="13">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0704690448476101</v>
+        <v>0.07046904484761005</v>
       </c>
     </row>
     <row r="14">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01203558210646722</v>
+        <v>0.0120355821064672</v>
       </c>
     </row>
     <row r="15">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4126004241262339</v>
+        <v>0.4126004241262338</v>
       </c>
     </row>
     <row r="16">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.7666451703313775</v>
+        <v>-0.7666451703313776</v>
       </c>
       <c r="C2" t="n">
         <v>0.4645690067847101</v>
@@ -642,10 +642,10 @@
         <v>0.2354465298658576</v>
       </c>
       <c r="E2" t="n">
-        <v>0.916659770640472</v>
+        <v>0.9166597706404719</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02704162110085874</v>
+        <v>0.02704162110085869</v>
       </c>
     </row>
     <row r="3">
@@ -658,16 +658,16 @@
         <v>-1.325040788015471</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2657921177348193</v>
+        <v>0.2657921177348191</v>
       </c>
       <c r="D3" t="n">
         <v>0.10170073758894</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6946404866353961</v>
+        <v>0.6946404866353959</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006864912721262834</v>
+        <v>0.006864912721262829</v>
       </c>
     </row>
     <row r="4">
@@ -677,16 +677,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-2.652581745763584</v>
+        <v>-2.652581745763585</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0704690448476101</v>
+        <v>0.07046904484761005</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01203558210646722</v>
+        <v>0.0120355821064672</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4126004241262339</v>
+        <v>0.4126004241262338</v>
       </c>
       <c r="F4" t="n">
         <v>0.003263680692093936</v>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3035692459935509</v>
+        <v>0.303569245993551</v>
       </c>
       <c r="C2" t="n">
         <v>-0.4858150606256127</v>
@@ -811,13 +811,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.09053496729843558</v>
+        <v>-0.09053496729843569</v>
       </c>
       <c r="C3" t="n">
         <v>-1.437721802399025</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1536022691023411</v>
+        <v>0.1536022691023406</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3490853798274802</v>
+        <v>0.3490853798274803</v>
       </c>
       <c r="C5" t="n">
         <v>-0.6128078723550465</v>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.2540539747143989</v>
+        <v>-0.2540539747143988</v>
       </c>
       <c r="C6" t="n">
         <v>0.3988564445182058</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5669879424213812</v>
+        <v>-0.5669879424213806</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1909304394969769</v>
+        <v>0.190930439496977</v>
       </c>
       <c r="C8" t="n">
         <v>-1.009660671247483</v>
@@ -1133,13 +1133,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1058668675511346</v>
+        <v>0.1058668675511344</v>
       </c>
       <c r="C10" t="n">
         <v>0.06590635973753277</v>
       </c>
       <c r="D10" t="n">
-        <v>1.019099448631348</v>
+        <v>1.019099448631347</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.3785271549791804</v>
+        <v>-0.3785271549791803</v>
       </c>
       <c r="C12" t="n">
         <v>-0.2161332986651115</v>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.5012702603247937</v>
+        <v>-0.5012702603247938</v>
       </c>
       <c r="C13" t="n">
         <v>0.9015926609919137</v>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.4000280024741704</v>
+        <v>-0.4000280024741703</v>
       </c>
       <c r="C14" t="n">
         <v>0.5547723214630254</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.210261511669544</v>
+        <v>-1.210261511669543</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1363,13 +1363,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1669232286961847</v>
+        <v>-0.1669232286961848</v>
       </c>
       <c r="C15" t="n">
         <v>0.3778066907030854</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1830230217943291</v>
+        <v>-0.1830230217943296</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>1.819469531538429</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3942189848706004</v>
+        <v>-0.3942189848706001</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.06489355131175095</v>
+        <v>-0.06489355131175106</v>
       </c>
       <c r="C18" t="n">
         <v>0.4757315244629794</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2665980220829762</v>
+        <v>0.2665980220829757</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0539602548203324</v>
+        <v>0.05396025482033245</v>
       </c>
       <c r="C19" t="n">
         <v>0.7294218893112417</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7903590860383856</v>
+        <v>0.7903590860383859</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1456968949337566</v>
+        <v>-0.1456968949337565</v>
       </c>
       <c r="C20" t="n">
         <v>0.5691912134699814</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.08948350869765193</v>
+        <v>-0.08948350869765143</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1989128906978095</v>
+        <v>-0.1989128906978094</v>
       </c>
       <c r="C22" t="n">
         <v>0.3462135391995458</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3239940175984097</v>
+        <v>-0.3239940175984092</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1731,13 +1731,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.191567206592782</v>
+        <v>0.1915672065927819</v>
       </c>
       <c r="C23" t="n">
         <v>-1.546183152102437</v>
       </c>
       <c r="D23" t="n">
-        <v>1.396760898597113</v>
+        <v>1.396760898597112</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3795170631755896</v>
+        <v>-0.3795170631755897</v>
       </c>
       <c r="C24" t="n">
         <v>0.1696529135920411</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1197571205511969</v>
+        <v>0.119757120551197</v>
       </c>
       <c r="C25" t="n">
         <v>-0.2268099651610779</v>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3409314871343583</v>
+        <v>-0.3409314871343582</v>
       </c>
       <c r="C27" t="n">
         <v>-0.1689490894384822</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9498369215134705</v>
+        <v>-0.9498369215134701</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2007,13 +2007,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1461892299385081</v>
+        <v>-0.1461892299385082</v>
       </c>
       <c r="C29" t="n">
         <v>-0.02968559881833521</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.09165311448734419</v>
+        <v>-0.09165311448734444</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1957735252430409</v>
+        <v>-0.195773525243041</v>
       </c>
       <c r="C30" t="n">
         <v>-0.0006623959568772099</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3101595646326616</v>
+        <v>-0.3101595646326621</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2145,13 +2145,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1405419733734229</v>
+        <v>-0.1405419733734231</v>
       </c>
       <c r="C32" t="n">
         <v>0.2351879475633289</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.06676696903508014</v>
+        <v>-0.06676696903508111</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.09783912785934068</v>
+        <v>-0.09783912785934062</v>
       </c>
       <c r="C33" t="n">
         <v>0.3038667126524351</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1214145333353491</v>
+        <v>0.1214145333353493</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.2353514648807941</v>
+        <v>-0.2353514648807942</v>
       </c>
       <c r="C37" t="n">
         <v>0.6271730023339054</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4845703340344913</v>
+        <v>-0.4845703340344918</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2467,13 +2467,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.01875336389815391</v>
+        <v>-0.01875336389815396</v>
       </c>
       <c r="C39" t="n">
         <v>-0.1178819236882987</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4699270902660447</v>
+        <v>0.4699270902660445</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.176800648574842</v>
+        <v>0.1768006485748421</v>
       </c>
       <c r="C41" t="n">
         <v>-0.6530130464183399</v>
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.1253328976907889</v>
+        <v>-0.125332897690789</v>
       </c>
       <c r="C42" t="n">
         <v>-0.5887043434061376</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0002558880407976535</v>
+        <v>0.0002558880407971643</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.251857537467223</v>
+        <v>0.2518575374672233</v>
       </c>
       <c r="C44" t="n">
         <v>-0.4562099652541439</v>
       </c>
       <c r="D44" t="n">
-        <v>1.662446355989435</v>
+        <v>1.662446355989436</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2881,13 +2881,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.2729567360682781</v>
+        <v>-0.272956736068278</v>
       </c>
       <c r="C48" t="n">
         <v>0.4113340895852979</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6502880126555679</v>
+        <v>-0.6502880126555675</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.4531076962497637</v>
+        <v>-0.4531076962497638</v>
       </c>
       <c r="C49" t="n">
         <v>0.8190497906720144</v>
       </c>
       <c r="D49" t="n">
-        <v>-1.444171369427371</v>
+        <v>-1.444171369427372</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>-0.09787546261339235</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.492094818603323</v>
+        <v>-1.492094818603322</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>

--- a/results/GSE186332/selinexor_proliferation_sensitivity_analysis.xlsx
+++ b/results/GSE186332/selinexor_proliferation_sensitivity_analysis.xlsx
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.006864912721262829</v>
+        <v>0.006864912721262816</v>
       </c>
     </row>
     <row r="13">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07046904484761005</v>
+        <v>0.0704690448476101</v>
       </c>
     </row>
     <row r="14">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0120355821064672</v>
+        <v>0.01203558210646722</v>
       </c>
     </row>
     <row r="15">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4126004241262338</v>
+        <v>0.4126004241262339</v>
       </c>
     </row>
     <row r="16">
@@ -642,7 +642,7 @@
         <v>0.2354465298658576</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9166597706404719</v>
+        <v>0.9166597706404718</v>
       </c>
       <c r="F2" t="n">
         <v>0.02704162110085869</v>
@@ -667,7 +667,7 @@
         <v>0.6946404866353959</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006864912721262829</v>
+        <v>0.006864912721262816</v>
       </c>
     </row>
     <row r="4">
@@ -677,16 +677,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-2.652581745763585</v>
+        <v>-2.652581745763584</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07046904484761005</v>
+        <v>0.0704690448476101</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0120355821064672</v>
+        <v>0.01203558210646722</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4126004241262338</v>
+        <v>0.4126004241262339</v>
       </c>
       <c r="F4" t="n">
         <v>0.003263680692093936</v>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.303569245993551</v>
+        <v>0.3035692459935511</v>
       </c>
       <c r="C2" t="n">
         <v>-0.4858150606256127</v>
@@ -811,13 +811,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.09053496729843569</v>
+        <v>-0.09053496729843552</v>
       </c>
       <c r="C3" t="n">
         <v>-1.437721802399025</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1536022691023406</v>
+        <v>0.1536022691023413</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.0006384040292134463</v>
+        <v>-0.0006384040292133353</v>
       </c>
       <c r="C4" t="n">
         <v>0.1791872673190783</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5497555026933404</v>
+        <v>0.5497555026933408</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>0.3988564445182058</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5669879424213806</v>
+        <v>-0.5669879424213808</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>0.7938781950718534</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8826594532747009</v>
+        <v>-0.882659453274701</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1041,13 +1041,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.190930439496977</v>
+        <v>0.1909304394969768</v>
       </c>
       <c r="C8" t="n">
         <v>-1.009660671247483</v>
       </c>
       <c r="D8" t="n">
-        <v>1.393954814194397</v>
+        <v>1.393954814194396</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02456567791523645</v>
+        <v>-0.02456567791523639</v>
       </c>
       <c r="C9" t="n">
         <v>-0.5746463972119965</v>
       </c>
       <c r="D9" t="n">
-        <v>0.444313575035014</v>
+        <v>0.4443135750350141</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1058668675511344</v>
+        <v>0.1058668675511345</v>
       </c>
       <c r="C10" t="n">
         <v>0.06590635973753277</v>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.3621064211877676</v>
+        <v>-0.3621064211877677</v>
       </c>
       <c r="C11" t="n">
         <v>-0.3029434700678931</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.043149928054247</v>
+        <v>-1.043149928054248</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1271,13 +1271,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.5012702603247938</v>
+        <v>-0.5012702603247936</v>
       </c>
       <c r="C13" t="n">
         <v>0.9015926609919137</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.656412580909693</v>
+        <v>-1.656412580909692</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.4000280024741703</v>
+        <v>-0.4000280024741701</v>
       </c>
       <c r="C14" t="n">
         <v>0.5547723214630254</v>
@@ -1369,7 +1369,7 @@
         <v>0.3778066907030854</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1830230217943296</v>
+        <v>-0.1830230217943297</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.2148486011203609</v>
+        <v>-0.214848601120361</v>
       </c>
       <c r="C16" t="n">
         <v>1.819469531538429</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3942189848706001</v>
+        <v>-0.3942189848706007</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.06489355131175106</v>
+        <v>-0.06489355131175095</v>
       </c>
       <c r="C18" t="n">
         <v>0.4757315244629794</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2665980220829757</v>
+        <v>0.2665980220829761</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.05396025482033245</v>
+        <v>0.05396025482033234</v>
       </c>
       <c r="C19" t="n">
         <v>0.7294218893112417</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7903590860383859</v>
+        <v>0.7903590860383852</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1456968949337565</v>
+        <v>-0.1456968949337566</v>
       </c>
       <c r="C20" t="n">
         <v>0.5691912134699814</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.08948350869765143</v>
+        <v>-0.08948350869765204</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.285845185822498</v>
+        <v>0.2858451858224981</v>
       </c>
       <c r="C21" t="n">
         <v>-0.5258996276885851</v>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1989128906978094</v>
+        <v>-0.1989128906978095</v>
       </c>
       <c r="C22" t="n">
         <v>0.3462135391995458</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3239940175984092</v>
+        <v>-0.3239940175984101</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1731,13 +1731,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1915672065927819</v>
+        <v>0.191567206592782</v>
       </c>
       <c r="C23" t="n">
         <v>-1.546183152102437</v>
       </c>
       <c r="D23" t="n">
-        <v>1.396760898597112</v>
+        <v>1.396760898597113</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1777,13 +1777,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3795170631755897</v>
+        <v>-0.3795170631755898</v>
       </c>
       <c r="C24" t="n">
         <v>0.1696529135920411</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.119874575488376</v>
+        <v>-1.119874575488377</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>0.2118292645818077</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8857822140406025</v>
+        <v>-0.8857822140406024</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>-0.1689490894384822</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9498369215134701</v>
+        <v>-0.9498369215134702</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2007,13 +2007,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1461892299385082</v>
+        <v>-0.1461892299385081</v>
       </c>
       <c r="C29" t="n">
         <v>-0.02968559881833521</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.09165311448734444</v>
+        <v>-0.09165311448734406</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>-0.0006623959568772099</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3101595646326621</v>
+        <v>-0.3101595646326622</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2897718616821827</v>
+        <v>-0.2897718616821825</v>
       </c>
       <c r="C31" t="n">
         <v>0.4961157560071276</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.724388358018468</v>
+        <v>-0.7243883580184671</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2145,13 +2145,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1405419733734231</v>
+        <v>-0.1405419733734229</v>
       </c>
       <c r="C32" t="n">
         <v>0.2351879475633289</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.06676696903508111</v>
+        <v>-0.0667669690350805</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>0.3038667126524351</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1214145333353493</v>
+        <v>0.1214145333353492</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>-0.8821813456855014</v>
       </c>
       <c r="D35" t="n">
-        <v>1.230232653521748</v>
+        <v>1.230232653521747</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>0.6215138439426001</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7129966652452815</v>
+        <v>-0.7129966652452816</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>0.6271730023339054</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4845703340344918</v>
+        <v>-0.484570334034492</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>-0.720307529875688</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5569933730109206</v>
+        <v>0.5569933730109203</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>-0.1178819236882987</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4699270902660445</v>
+        <v>0.4699270902660443</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1768006485748421</v>
+        <v>0.176800648574842</v>
       </c>
       <c r="C41" t="n">
         <v>-0.6530130464183399</v>
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.125332897690789</v>
+        <v>-0.1253328976907889</v>
       </c>
       <c r="C42" t="n">
         <v>-0.5887043434061376</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0002558880407971643</v>
+        <v>0.0002558880407975312</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2651,13 +2651,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.172338913748451</v>
+        <v>-0.1723389137484508</v>
       </c>
       <c r="C43" t="n">
         <v>1.332978640440253</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2068886854809439</v>
+        <v>-0.2068886854809432</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2518575374672233</v>
+        <v>0.251857537467223</v>
       </c>
       <c r="C44" t="n">
         <v>-0.4562099652541439</v>
       </c>
       <c r="D44" t="n">
-        <v>1.662446355989436</v>
+        <v>1.662446355989434</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.1266908976462644</v>
+        <v>-0.1266908976462642</v>
       </c>
       <c r="C45" t="n">
         <v>-0.3099088589278771</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.00572850172910837</v>
+        <v>-0.005728501729107759</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2789,13 +2789,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.1656100261516482</v>
+        <v>-0.1656100261516483</v>
       </c>
       <c r="C46" t="n">
         <v>0.07426114607454079</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1772360437891734</v>
+        <v>-0.177236043789174</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2835,13 +2835,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.02074949506060797</v>
+        <v>-0.02074949506060808</v>
       </c>
       <c r="C47" t="n">
         <v>-0.1120333472702057</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4611306047729372</v>
+        <v>0.4611306047729365</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>0.4113340895852979</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6502880126555675</v>
+        <v>-0.6502880126555676</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.4531076962497638</v>
+        <v>-0.4531076962497637</v>
       </c>
       <c r="C49" t="n">
         <v>0.8190497906720144</v>
@@ -2979,7 +2979,7 @@
         <v>0.1544321174350495</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.6321605150517657</v>
+        <v>-0.6321605150517658</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -3019,13 +3019,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.4639826633474022</v>
+        <v>-0.4639826633474023</v>
       </c>
       <c r="C51" t="n">
         <v>-0.09787546261339235</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.492094818603322</v>
+        <v>-1.492094818603323</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>-0.1613341681448813</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.9818298904967258</v>
+        <v>-0.9818298904967259</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -3111,13 +3111,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.329928948359771</v>
+        <v>-0.3299289483597709</v>
       </c>
       <c r="C53" t="n">
         <v>0.3979531232292181</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.9013512936456988</v>
+        <v>-0.9013512936456984</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
